--- a/SGC-CKN/Excel/c4921e31-354a-4b04-a564-7319e0c5b362_Lô_đất_ký_hiệu_CT-02_P7-162_D800_18-01-2026.xlsx
+++ b/SGC-CKN/Excel/c4921e31-354a-4b04-a564-7319e0c5b362_Lô_đất_ký_hiệu_CT-02_P7-162_D800_18-01-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="76">
   <si>
     <t>Dự án</t>
   </si>
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>20:00 17/01/2026</t>
+    <t>20:00 17/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>05:32 18/01/2026</t>
+    <t>05:32 18/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -99,126 +99,122 @@
   </si>
   <si>
     <t xml:space="preserve">20:00
-17/01/2026</t>
+17/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:28
+17/03/2026</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:29
+17/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">20:40
-17/01/2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+17/03/2026</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">20:41
-17/01/2026</t>
+17/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">21:35
-17/01/2026</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>Sét xám trắng, xám xanh dẻo chảy</t>
+17/03/2026</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">21:36
-17/01/2026</t>
+17/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">22:32
-17/01/2026</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+17/03/2026</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">22:33
-17/01/2026</t>
+17/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">23:35
-17/01/2026</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+17/03/2026</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">23:36
-17/01/2026</t>
+17/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">00:35
-18/01/2026</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+18/03/2026</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">00:36
-18/01/2026</t>
+18/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">01:25
-18/01/2026</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01:45
-18/01/2026</t>
+18/03/2026</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>TK-16.1. Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">02:59
-18/01/2026</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>TK-16.1. Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
+18/03/2026</t>
+  </si>
+  <si>
+    <t>Ước lượng thời gian từ khoảng gộp 03:00 - 05:05</t>
+  </si>
+  <si>
+    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">03:00
-18/01/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04:00
-18/01/2026</t>
-  </si>
-  <si>
-    <t>Ước lượng thời gian từ khoảng gộp 03:00 - 05:05</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04:01
-18/01/2026</t>
+18/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">05:05
-18/01/2026</t>
+18/03/2026</t>
   </si>
   <si>
     <t>17</t>
@@ -228,11 +224,11 @@
   </si>
   <si>
     <t xml:space="preserve">05:10
-18/01/2026</t>
+18/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">05:32
-18/01/2026</t>
+18/03/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -391,7 +387,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -406,12 +402,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFFECACA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFECACA"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -581,17 +577,17 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1239,19 +1235,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.67</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-6.94</v>
       </c>
       <c r="H11" s="5">
-        <v>0.67</v>
+        <v>0.47</v>
       </c>
       <c r="I11" s="5">
-        <v>3.27</v>
+        <v>6.94</v>
       </c>
       <c r="J11" s="8">
-        <v>4.91</v>
+        <v>14.87</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1280,13 +1276,13 @@
         <v>-9.04</v>
       </c>
       <c r="H12" s="9">
-        <v>0.9</v>
+        <v>0.18</v>
       </c>
       <c r="I12" s="9">
         <v>2.1</v>
       </c>
       <c r="J12" s="8">
-        <v>2.33</v>
+        <v>11.45</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1312,53 +1308,53 @@
         <v>-9.04</v>
       </c>
       <c r="G13" s="12">
-        <v>-17.21</v>
+        <v>-17.24</v>
       </c>
       <c r="H13" s="12">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="I13" s="12">
-        <v>8.17</v>
-      </c>
-      <c r="J13" s="15">
-        <v>8.75</v>
+        <v>8.2</v>
+      </c>
+      <c r="J13" s="8">
+        <v>9.11</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="16">
-        <v>-17.21</v>
-      </c>
-      <c r="G14" s="16">
+      <c r="F14" s="15">
+        <v>-17.24</v>
+      </c>
+      <c r="G14" s="15">
         <v>-21.54</v>
       </c>
-      <c r="H14" s="16">
-        <v>1.03</v>
-      </c>
-      <c r="I14" s="16">
-        <v>4.33</v>
-      </c>
-      <c r="J14" s="8">
-        <v>4.19</v>
-      </c>
-      <c r="K14" s="17" t="s">
+      <c r="H14" s="15">
+        <v>0.93</v>
+      </c>
+      <c r="I14" s="15">
+        <v>4.3</v>
+      </c>
+      <c r="J14" s="18">
+        <v>4.61</v>
+      </c>
+      <c r="K14" s="16" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1382,16 +1378,16 @@
         <v>-21.54</v>
       </c>
       <c r="G15" s="19">
-        <v>-25.84</v>
+        <v>-25.54</v>
       </c>
       <c r="H15" s="19">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="I15" s="19">
-        <v>4.3</v>
-      </c>
-      <c r="J15" s="8">
-        <v>4.37</v>
+        <v>4</v>
+      </c>
+      <c r="J15" s="18">
+        <v>3.87</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1414,19 +1410,19 @@
         <v>50</v>
       </c>
       <c r="F16" s="22">
-        <v>-25.84</v>
+        <v>-25.54</v>
       </c>
       <c r="G16" s="22">
         <v>-35.64</v>
       </c>
       <c r="H16" s="22">
-        <v>0.82</v>
+        <v>0.98</v>
       </c>
       <c r="I16" s="22">
-        <v>9.8</v>
-      </c>
-      <c r="J16" s="15">
-        <v>12</v>
+        <v>10.1</v>
+      </c>
+      <c r="J16" s="8">
+        <v>10.27</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1455,13 +1451,13 @@
         <v>-37.85</v>
       </c>
       <c r="H17" s="25">
-        <v>1.23</v>
+        <v>0.82</v>
       </c>
       <c r="I17" s="25">
         <v>2.21</v>
       </c>
-      <c r="J17" s="8">
-        <v>1.79</v>
+      <c r="J17" s="18">
+        <v>2.71</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1478,10 +1474,10 @@
         <v>56</v>
       </c>
       <c r="D18" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>57</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>58</v>
       </c>
       <c r="F18" s="28">
         <v>-37.85</v>
@@ -1490,16 +1486,16 @@
         <v>-39.5</v>
       </c>
       <c r="H18" s="28">
-        <v>1</v>
+        <v>1.57</v>
       </c>
       <c r="I18" s="28">
         <v>1.65</v>
       </c>
-      <c r="J18" s="8">
-        <v>1.65</v>
+      <c r="J18" s="18">
+        <v>1.05</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1510,13 +1506,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="E19" s="33" t="s">
         <v>61</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>62</v>
       </c>
       <c r="F19" s="31">
         <v>-39.5</v>
@@ -1525,48 +1521,48 @@
         <v>-44.15</v>
       </c>
       <c r="H19" s="31">
-        <v>1.07</v>
+        <v>2.08</v>
       </c>
       <c r="I19" s="31">
         <v>4.65</v>
       </c>
-      <c r="J19" s="8">
-        <v>4.36</v>
+      <c r="J19" s="18">
+        <v>2.23</v>
       </c>
       <c r="K19" s="32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="36" t="s">
+      <c r="E20" s="36" t="s">
         <v>65</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>66</v>
       </c>
       <c r="F20" s="34">
         <v>-44.15</v>
       </c>
       <c r="G20" s="34">
-        <v>-45.07</v>
+        <v>-45.09</v>
       </c>
       <c r="H20" s="34">
         <v>0.37</v>
       </c>
       <c r="I20" s="34">
-        <v>0.92</v>
-      </c>
-      <c r="J20" s="8">
-        <v>2.51</v>
+        <v>0.94</v>
+      </c>
+      <c r="J20" s="18">
+        <v>2.56</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
@@ -1574,7 +1570,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1680,31 +1676,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1721,19 +1717,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.67</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-6.94</v>
       </c>
       <c r="G2" s="5">
-        <v>0.67</v>
+        <v>0.47</v>
       </c>
       <c r="H2" s="5">
-        <v>3.27</v>
+        <v>6.94</v>
       </c>
       <c r="I2" s="8">
-        <v>4.91</v>
+        <v>14.87</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1756,13 +1752,13 @@
         <v>-9.04</v>
       </c>
       <c r="G3" s="9">
-        <v>0.9</v>
+        <v>0.18</v>
       </c>
       <c r="H3" s="9">
         <v>2.1</v>
       </c>
       <c r="I3" s="8">
-        <v>2.33</v>
+        <v>11.45</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1782,45 +1778,45 @@
         <v>-9.04</v>
       </c>
       <c r="F4" s="12">
-        <v>-17.21</v>
+        <v>-17.24</v>
       </c>
       <c r="G4" s="12">
+        <v>0.9</v>
+      </c>
+      <c r="H4" s="12">
+        <v>8.2</v>
+      </c>
+      <c r="I4" s="8">
+        <v>9.11</v>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
+        <v>4</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="15">
+        <v>1</v>
+      </c>
+      <c r="E5" s="15">
+        <v>-17.24</v>
+      </c>
+      <c r="F5" s="15">
+        <v>-21.54</v>
+      </c>
+      <c r="G5" s="15">
         <v>0.93</v>
       </c>
-      <c r="H4" s="12">
-        <v>8.17</v>
-      </c>
-      <c r="I4" s="15">
-        <v>8.75</v>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
-        <v>4</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="16">
-        <v>1</v>
-      </c>
-      <c r="E5" s="16">
-        <v>-17.21</v>
-      </c>
-      <c r="F5" s="16">
-        <v>-21.54</v>
-      </c>
-      <c r="G5" s="16">
-        <v>1.03</v>
-      </c>
-      <c r="H5" s="16">
-        <v>4.33</v>
-      </c>
-      <c r="I5" s="8">
-        <v>4.19</v>
+      <c r="H5" s="15">
+        <v>4.3</v>
+      </c>
+      <c r="I5" s="18">
+        <v>4.61</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1840,16 +1836,16 @@
         <v>-21.54</v>
       </c>
       <c r="F6" s="19">
-        <v>-25.84</v>
+        <v>-25.54</v>
       </c>
       <c r="G6" s="19">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="H6" s="19">
-        <v>4.3</v>
-      </c>
-      <c r="I6" s="8">
-        <v>4.37</v>
+        <v>4</v>
+      </c>
+      <c r="I6" s="18">
+        <v>3.87</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1866,19 +1862,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-25.84</v>
+        <v>-25.54</v>
       </c>
       <c r="F7" s="22">
         <v>-35.64</v>
       </c>
       <c r="G7" s="22">
-        <v>0.82</v>
+        <v>0.98</v>
       </c>
       <c r="H7" s="22">
-        <v>9.8</v>
-      </c>
-      <c r="I7" s="15">
-        <v>12</v>
+        <v>10.1</v>
+      </c>
+      <c r="I7" s="8">
+        <v>10.27</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1901,13 +1897,13 @@
         <v>-37.85</v>
       </c>
       <c r="G8" s="25">
-        <v>1.23</v>
+        <v>0.82</v>
       </c>
       <c r="H8" s="25">
         <v>2.21</v>
       </c>
-      <c r="I8" s="8">
-        <v>1.79</v>
+      <c r="I8" s="18">
+        <v>2.71</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1930,13 +1926,13 @@
         <v>-39.5</v>
       </c>
       <c r="G9" s="28">
-        <v>1</v>
+        <v>1.57</v>
       </c>
       <c r="H9" s="28">
         <v>1.65</v>
       </c>
-      <c r="I9" s="8">
-        <v>1.65</v>
+      <c r="I9" s="18">
+        <v>1.05</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1947,7 +1943,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1959,13 +1955,13 @@
         <v>-44.15</v>
       </c>
       <c r="G10" s="31">
-        <v>1.07</v>
+        <v>2.08</v>
       </c>
       <c r="H10" s="31">
         <v>4.65</v>
       </c>
-      <c r="I10" s="8">
-        <v>4.36</v>
+      <c r="I10" s="18">
+        <v>2.23</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1976,7 +1972,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -1985,21 +1981,21 @@
         <v>-44.15</v>
       </c>
       <c r="F11" s="34">
-        <v>-45.07</v>
+        <v>-45.09</v>
       </c>
       <c r="G11" s="34">
         <v>0.37</v>
       </c>
       <c r="H11" s="34">
-        <v>0.92</v>
-      </c>
-      <c r="I11" s="8">
-        <v>2.51</v>
+        <v>0.94</v>
+      </c>
+      <c r="I11" s="18">
+        <v>2.56</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
@@ -2011,19 +2007,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>-3.67</v>
+        <v>0</v>
       </c>
       <c r="F12" s="39">
-        <v>-45.07</v>
+        <v>-45.09</v>
       </c>
       <c r="G12" s="39">
-        <v>9</v>
+        <v>9.33</v>
       </c>
       <c r="H12" s="39">
-        <v>41.4</v>
+        <v>45.09</v>
       </c>
       <c r="I12" s="39">
-        <v>4.6</v>
+        <v>4.83</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/c4921e31-354a-4b04-a564-7319e0c5b362_Lô_đất_ký_hiệu_CT-02_P7-162_D800_18-01-2026.xlsx
+++ b/SGC-CKN/Excel/c4921e31-354a-4b04-a564-7319e0c5b362_Lô_đất_ký_hiệu_CT-02_P7-162_D800_18-01-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="77">
   <si>
     <t>Dự án</t>
   </si>
@@ -197,6 +197,10 @@
   </si>
   <si>
     <t>TK-16.1. Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:45
+18/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">02:59
@@ -1474,10 +1478,10 @@
         <v>56</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F18" s="28">
         <v>-37.85</v>
@@ -1486,16 +1490,16 @@
         <v>-39.5</v>
       </c>
       <c r="H18" s="28">
-        <v>1.57</v>
+        <v>1.23</v>
       </c>
       <c r="I18" s="28">
         <v>1.65</v>
       </c>
       <c r="J18" s="18">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1506,13 +1510,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F19" s="31">
         <v>-39.5</v>
@@ -1530,24 +1534,24 @@
         <v>2.23</v>
       </c>
       <c r="K19" s="32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F20" s="34">
         <v>-44.15</v>
@@ -1570,7 +1574,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1676,31 +1680,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1926,13 +1930,13 @@
         <v>-39.5</v>
       </c>
       <c r="G9" s="28">
-        <v>1.57</v>
+        <v>1.23</v>
       </c>
       <c r="H9" s="28">
         <v>1.65</v>
       </c>
       <c r="I9" s="18">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1943,7 +1947,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1972,7 +1976,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -1995,7 +1999,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
@@ -2013,13 +2017,13 @@
         <v>-45.09</v>
       </c>
       <c r="G12" s="39">
-        <v>9.33</v>
+        <v>9</v>
       </c>
       <c r="H12" s="39">
         <v>45.09</v>
       </c>
       <c r="I12" s="39">
-        <v>4.83</v>
+        <v>5.01</v>
       </c>
     </row>
   </sheetData>
